--- a/results/BMW_2020_classified.xlsx
+++ b/results/BMW_2020_classified.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c5b0ba968cd3026a/Documents/thesis-greenwashing/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_28518FE72824509661E14C3625101254AD04C3DE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F279CD88-028F-47F1-8F02-B8504F149540}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_28518FE72824509661E14C3625101254AD04C3DE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6817E93A-AC9F-42F5-9EFA-1462AF2E3AA4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
